--- a/ventas_electrodomesticos_preparados.xlsx
+++ b/ventas_electrodomesticos_preparados.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,9 +50,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,6 +421,28 @@
   </sheetPr>
   <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -530,7 +552,7 @@
           <t>V001</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +636,7 @@
           <t>V002</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>46235</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,7 +720,7 @@
           <t>V003</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>46236</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -782,7 +804,7 @@
           <t>V004</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46236</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -866,7 +888,7 @@
           <t>V005</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,7 +972,7 @@
           <t>V006</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1034,7 +1056,7 @@
           <t>V007</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1118,7 +1140,7 @@
           <t>V008</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1202,7 +1224,7 @@
           <t>V009</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1286,7 +1308,7 @@
           <t>V010</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1370,7 +1392,7 @@
           <t>V011</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1454,7 +1476,7 @@
           <t>V012</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1538,7 +1560,7 @@
           <t>V013</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1622,7 +1644,7 @@
           <t>V014</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1706,7 +1728,7 @@
           <t>V015</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>46242</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1750,7 +1772,6 @@
       <c r="K16" t="n">
         <v>210000</v>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Transferencia</t>
@@ -1775,8 +1796,6 @@
       <c r="R16" t="n">
         <v>210000</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1784,7 +1803,7 @@
           <t>V016</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>46242</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1868,7 +1887,7 @@
           <t>V017</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>46243</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1952,7 +1971,7 @@
           <t>V018</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>46243</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -2036,7 +2055,7 @@
           <t>V019</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -2120,7 +2139,7 @@
           <t>V020</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -2185,7 +2204,6 @@
           <t>Cancelada</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>138000</v>
       </c>
@@ -2202,7 +2220,7 @@
           <t>V021</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46245</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -2286,7 +2304,7 @@
           <t>V022</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46245</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -2370,7 +2388,7 @@
           <t>V023</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46246</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -2454,7 +2472,7 @@
           <t>V024</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46246</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -2519,7 +2537,6 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>740000</v>
       </c>
@@ -2536,7 +2553,7 @@
           <t>V025</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46247</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -2620,7 +2637,7 @@
           <t>V026</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46247</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -2704,7 +2721,7 @@
           <t>V027</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -2788,7 +2805,7 @@
           <t>V028</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -2872,7 +2889,7 @@
           <t>V029</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>46249</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -2956,7 +2973,7 @@
           <t>V030</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>46249</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -3040,7 +3057,7 @@
           <t>V031</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>46250</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -3124,7 +3141,7 @@
           <t>V032</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>46250</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -3171,7 +3188,6 @@
       <c r="L33" t="n">
         <v>0.11</v>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Particular</t>
@@ -3204,7 +3220,7 @@
           <t>V033</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46251</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -3288,7 +3304,7 @@
           <t>V034</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>46251</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -3372,7 +3388,7 @@
           <t>V035</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>46252</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -3456,7 +3472,7 @@
           <t>V036</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>46252</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -3547,6 +3563,12 @@
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3647,6 +3669,12 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
